--- a/flights/flights.xlsx
+++ b/flights/flights.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bansal_s\PyCharmMiscProject\Day 39 Flight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bansal_s\PyCharmMiscProject\scheduled-tasks\flights\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDB4AB3-F8C7-4F36-B7B3-367832F93A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6CECE6-A080-4325-BB75-67D4D56DE473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Start</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>MAA</t>
+  </si>
+  <si>
+    <t>DEL</t>
   </si>
 </sst>
 </file>
@@ -374,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -405,6 +408,17 @@
         <v>4000</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>5000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
